--- a/TEMPLATE THUNDERSTORM.xlsx
+++ b/TEMPLATE THUNDERSTORM.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F351C72C-1A75-4506-99F5-286F461EB1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118393EE-6D10-4394-871C-B196C4851597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -175,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -359,43 +359,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="double">
         <color indexed="64"/>
       </right>
@@ -412,7 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -472,40 +435,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -885,7 +839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -897,113 +851,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
       <c r="AG1" s="22"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
     </row>
     <row r="4" spans="1:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1043,97 +997,97 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>1</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>2</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <v>3</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <v>4</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="26">
         <v>5</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="26">
         <v>6</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="26">
         <v>7</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="26">
         <v>8</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="26">
         <v>9</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="26">
         <v>10</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="26">
         <v>11</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="26">
         <v>12</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="26">
         <v>13</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="26">
         <v>14</v>
       </c>
-      <c r="P5" s="27">
+      <c r="P5" s="26">
         <v>15</v>
       </c>
-      <c r="Q5" s="27">
+      <c r="Q5" s="26">
         <v>16</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="26">
         <v>17</v>
       </c>
-      <c r="S5" s="27">
+      <c r="S5" s="26">
         <v>18</v>
       </c>
-      <c r="T5" s="27">
+      <c r="T5" s="26">
         <v>19</v>
       </c>
-      <c r="U5" s="27">
+      <c r="U5" s="26">
         <v>20</v>
       </c>
-      <c r="V5" s="27">
+      <c r="V5" s="26">
         <v>21</v>
       </c>
-      <c r="W5" s="27">
+      <c r="W5" s="26">
         <v>22</v>
       </c>
-      <c r="X5" s="27">
+      <c r="X5" s="26">
         <v>23</v>
       </c>
-      <c r="Y5" s="27">
+      <c r="Y5" s="26">
         <v>24</v>
       </c>
-      <c r="Z5" s="27">
+      <c r="Z5" s="26">
         <v>25</v>
       </c>
-      <c r="AA5" s="27">
+      <c r="AA5" s="26">
         <v>26</v>
       </c>
-      <c r="AB5" s="27">
+      <c r="AB5" s="26">
         <v>27</v>
       </c>
-      <c r="AC5" s="27">
+      <c r="AC5" s="26">
         <v>28</v>
       </c>
-      <c r="AD5" s="27">
+      <c r="AD5" s="26">
         <v>29</v>
       </c>
-      <c r="AE5" s="27">
+      <c r="AE5" s="26">
         <v>30</v>
       </c>
-      <c r="AF5" s="33">
+      <c r="AF5" s="28">
         <v>31</v>
       </c>
     </row>
@@ -1141,37 +1095,37 @@
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="34"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="29"/>
     </row>
     <row r="7" spans="1:33" ht="16.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -1207,7 +1161,7 @@
       <c r="AC7" s="17"/>
       <c r="AD7" s="17"/>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="14"/>
+      <c r="AF7" s="15"/>
     </row>
     <row r="8" spans="1:33" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
@@ -1241,9 +1195,9 @@
       <c r="AA8" s="5"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="5"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="32"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="14"/>
     </row>
     <row r="9" spans="1:33" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -1842,47 +1796,21 @@
       <c r="AE30" s="11"/>
     </row>
     <row r="31" spans="1:32" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="V31" s="29" t="s">
+      <c r="V31" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="29"/>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="V31:AE31"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AD5:AD6"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
+  <mergeCells count="35">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A2:AF2"/>
     <mergeCell ref="A3:AF3"/>
@@ -1893,6 +1821,31 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="V31:AE31"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="Z5:Z6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.74803149606299213" right="0.23622047244094491" top="0.74803149606299213" bottom="0.23622047244094491" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1903,7 +1856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
@@ -1913,7 +1866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
